--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319650.2816502029</v>
+        <v>322259.061560525</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>2989156.853416513</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745722</v>
+        <v>20349704.61069184</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813076.283068547</v>
+        <v>4821032.195206849</v>
       </c>
     </row>
     <row r="11">
@@ -892,22 +892,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>10.61706312961832</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -974,19 +974,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.6263639150735023</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1211,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1262,13 +1262,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2741920426674804</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1402,19 +1402,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,25 +1560,25 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1609,13 +1609,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1645,25 +1645,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="15">
@@ -1682,22 +1682,22 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,19 +1794,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2031,31 +2031,31 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>19.30102689107961</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2080,19 +2080,19 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>81.00537765493296</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2207,16 +2207,16 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>224.9485118167893</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2308,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2350,22 +2350,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>135.1048497061963</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>111.1751113141406</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2438,22 +2438,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>47.02492433367362</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2542,22 +2542,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>35.69115069765793</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
@@ -2684,13 +2684,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>29.75784556612239</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2715,49 +2715,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2791,19 +2791,19 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>200.3235106453875</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.75784556612239</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>75.58265010978022</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2937,61 +2937,61 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3019,19 +3019,19 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>29.85921600351676</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>189.3719999999999</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3149,22 +3149,22 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>209.0513475444858</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X33" t="n">
-        <v>185.2613580987165</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3253,19 +3253,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>22.8280347615265</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3274,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>189.3719999999999</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3544,16 +3544,16 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>179.3813007854552</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="V38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3626,19 +3626,19 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X39" t="n">
-        <v>198.6893042226956</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>22.0339917726842</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3742,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
-        <v>184.1237416288039</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3806,31 +3806,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40.15828262684081</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3866,16 +3866,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>195.6353698080211</v>
       </c>
     </row>
     <row r="43">
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.47474747474747</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="C8" t="n">
-        <v>25.2121212121212</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M8" t="n">
-        <v>78.26000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O8" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="Y8" t="n">
-        <v>77.73737373737373</v>
+        <v>14.75230336596039</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L9" t="n">
-        <v>53.56</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M9" t="n">
-        <v>79.3</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N9" t="n">
-        <v>79.3</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O9" t="n">
-        <v>79.3</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P9" t="n">
-        <v>79.3</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>54.60525252525252</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G10" t="n">
-        <v>103.3623149756393</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.30000000000007</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348993</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R10" t="n">
-        <v>103.6392766348993</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S10" t="n">
-        <v>103.6392766348993</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>77.73737373737373</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>25.2121212121212</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M11" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N11" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M12" t="n">
-        <v>26.78000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.3623149756393</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R13" t="n">
-        <v>77.09968871301299</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S13" t="n">
-        <v>50.83706245038672</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T13" t="n">
-        <v>24.57443618776046</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U13" t="n">
-        <v>24.57443618776046</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V13" t="n">
-        <v>24.57443618776046</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="W13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54.60525252525252</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="C14" t="n">
-        <v>54.60525252525252</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="D14" t="n">
-        <v>54.60525252525252</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E14" t="n">
-        <v>54.60525252525252</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F14" t="n">
-        <v>54.60525252525252</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G14" t="n">
-        <v>54.60525252525252</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M14" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>54.60525252525252</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>54.60525252525252</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>54.60525252525252</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="X14" t="n">
-        <v>54.60525252525252</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="Y14" t="n">
-        <v>54.60525252525252</v>
+        <v>53.80778732512771</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="E15" t="n">
-        <v>80.86787878787879</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="F15" t="n">
-        <v>54.60525252525252</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="G15" t="n">
-        <v>28.34262626262626</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L15" t="n">
-        <v>53.56</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M15" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N15" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O15" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>2.80375594835618</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>87.08848484848485</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>57.68</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N17" t="n">
-        <v>57.68</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L18" t="n">
-        <v>29.96</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M18" t="n">
-        <v>29.96</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>29.96</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>106.5844716071511</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>78.30164332432284</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>50.01881504149456</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>21.73598675866627</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="C20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="D20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="E20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="F20" t="n">
-        <v>718.7505955256626</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G20" t="n">
-        <v>475.3162520913191</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H20" t="n">
-        <v>231.8819086569757</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="U20" t="n">
-        <v>720.5656565656566</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="V20" t="n">
-        <v>720.5656565656566</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="W20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="X20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="Y20" t="n">
-        <v>720.5656565656566</v>
+        <v>243.9530410142718</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>19.28</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M21" t="n">
-        <v>234.7819638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>454.2610177718119</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>227.0402987649539</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>227.0402987649539</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C23" t="n">
-        <v>962.184938960006</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D23" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>360.1724425458239</v>
+        <v>131.5792353467183</v>
       </c>
       <c r="C24" t="n">
-        <v>360.1724425458239</v>
+        <v>131.5792353467183</v>
       </c>
       <c r="D24" t="n">
-        <v>360.1724425458239</v>
+        <v>131.5792353467183</v>
       </c>
       <c r="E24" t="n">
-        <v>223.7028973880499</v>
+        <v>131.5792353467183</v>
       </c>
       <c r="F24" t="n">
-        <v>223.7028973880499</v>
+        <v>131.5792353467183</v>
       </c>
       <c r="G24" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>374.6006659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T24" t="n">
-        <v>588.3960608094349</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U24" t="n">
-        <v>360.1724425458239</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V24" t="n">
-        <v>360.1724425458239</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="W24" t="n">
-        <v>360.1724425458239</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="X24" t="n">
-        <v>360.1724425458239</v>
+        <v>339.3395341116723</v>
       </c>
       <c r="Y24" t="n">
-        <v>360.1724425458239</v>
+        <v>131.5792353467183</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C26" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X26" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y26" t="n">
-        <v>477.1313131313132</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.28</v>
+        <v>256.869462878957</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>256.869462878957</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>256.869462878957</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>256.869462878957</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>928.0054881392646</v>
       </c>
       <c r="U27" t="n">
-        <v>735.7763817363891</v>
+        <v>699.7818698756537</v>
       </c>
       <c r="V27" t="n">
-        <v>500.6242735046464</v>
+        <v>464.6297616439109</v>
       </c>
       <c r="W27" t="n">
-        <v>257.1899300703029</v>
+        <v>464.6297616439109</v>
       </c>
       <c r="X27" t="n">
-        <v>49.33842986477009</v>
+        <v>464.6297616439109</v>
       </c>
       <c r="Y27" t="n">
-        <v>19.28</v>
+        <v>256.869462878957</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>964</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C29" t="n">
-        <v>964</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="D29" t="n">
-        <v>964</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E29" t="n">
-        <v>964</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F29" t="n">
-        <v>720.5656565656566</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G29" t="n">
-        <v>477.1313131313132</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H29" t="n">
-        <v>233.6969696969697</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I29" t="n">
-        <v>31.34998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X29" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y29" t="n">
-        <v>964</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>268.0306603177695</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>93.57763103664249</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>93.57763103664249</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>93.57763103664249</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>93.57763103664249</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L30" t="n">
-        <v>248.2299999999999</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="M30" t="n">
-        <v>486.8199999999999</v>
+        <v>183.0578391930369</v>
       </c>
       <c r="N30" t="n">
-        <v>725.41</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O30" t="n">
-        <v>964</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="W30" t="n">
-        <v>257.1899300703029</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X30" t="n">
-        <v>49.33842986477009</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y30" t="n">
-        <v>49.33842986477009</v>
+        <v>436.2459973378375</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>425.6565656565656</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="C32" t="n">
-        <v>425.6565656565656</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="D32" t="n">
-        <v>425.6565656565656</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E32" t="n">
-        <v>425.6565656565656</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>506.5265183822256</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>712.3810405894649</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="U32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="V32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="W32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="X32" t="n">
-        <v>642.8282828282828</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="Y32" t="n">
-        <v>425.6565656565656</v>
+        <v>700.1014279485831</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C33" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D33" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E33" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F33" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M33" t="n">
-        <v>395.1119638733197</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="N33" t="n">
-        <v>607.9619638733197</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="O33" t="n">
-        <v>607.9619638733197</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T33" t="n">
-        <v>657.813405358766</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U33" t="n">
-        <v>657.813405358766</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V33" t="n">
-        <v>657.813405358766</v>
+        <v>650.4130134144505</v>
       </c>
       <c r="W33" t="n">
-        <v>657.813405358766</v>
+        <v>432.843318785129</v>
       </c>
       <c r="X33" t="n">
-        <v>470.6807204105675</v>
+        <v>224.9918185795962</v>
       </c>
       <c r="Y33" t="n">
-        <v>470.6807204105675</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.2</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="C35" t="n">
-        <v>17.2</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>264.9620386899402</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>29.30150906172561</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>504.9505276501126</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N35" t="n">
-        <v>710.8050498573519</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="U35" t="n">
-        <v>849.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="V35" t="n">
-        <v>632.7366674600557</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="W35" t="n">
-        <v>632.7366674600557</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="X35" t="n">
-        <v>415.5649502883385</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="Y35" t="n">
-        <v>198.3932331166214</v>
+        <v>700.1014279485831</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>221.45</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="M36" t="n">
-        <v>434.3</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V36" t="n">
-        <v>425.6565656565656</v>
+        <v>426.43660147347</v>
       </c>
       <c r="W36" t="n">
-        <v>208.4848484848484</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="X36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="C38" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>504.9505276501126</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N38" t="n">
-        <v>710.8050498573519</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T38" t="n">
-        <v>668.7151515151515</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="U38" t="n">
-        <v>668.7151515151515</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="V38" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="W38" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="X38" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="Y38" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M39" t="n">
-        <v>568.2575600578374</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N39" t="n">
-        <v>781.1075600578374</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="O39" t="n">
-        <v>860</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U39" t="n">
-        <v>642.8282828282828</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V39" t="n">
-        <v>642.8282828282828</v>
+        <v>426.43660147347</v>
       </c>
       <c r="W39" t="n">
-        <v>425.6565656565656</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="X39" t="n">
-        <v>224.9602987649539</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F40" t="n">
-        <v>770.2187030436354</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>770.2187030436354</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>770.2187030436354</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>770.2187030436354</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>747.9621456974897</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>857.2510699645388</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y40" t="n">
-        <v>770.2187030436354</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>630.7770012113231</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="C41" t="n">
-        <v>630.7770012113231</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="D41" t="n">
-        <v>630.7770012113231</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>630.7770012113231</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>630.7770012113231</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="G41" t="n">
-        <v>415.6254860598079</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>229.6419086569757</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>107.2817095536563</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>287.3575611383148</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>498.6475821194843</v>
       </c>
       <c r="N41" t="n">
-        <v>716.8553797028203</v>
+        <v>704.5021043267236</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Y41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>603.5845779491734</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C42" t="n">
-        <v>429.1315486680464</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>429.1315486680464</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>269.8940936625909</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>269.8940936625909</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>131.1632682452064</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>17.04</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>227.91</v>
+        <v>459.7635558748512</v>
       </c>
       <c r="N42" t="n">
-        <v>438.78</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="O42" t="n">
-        <v>649.65</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="P42" t="n">
-        <v>832.2934776133509</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V42" t="n">
-        <v>852</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>852</v>
+        <v>422.536925949487</v>
       </c>
       <c r="X42" t="n">
-        <v>644.1484997944672</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="Y42" t="n">
-        <v>644.1484997944672</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
     </row>
     <row r="44">
@@ -8196,22 +8196,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L5" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M5" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O5" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8281,19 +8281,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O6" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8357,16 +8357,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N7" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O7" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P7" t="n">
         <v>135.0065633140411</v>
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N8" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P8" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,16 +8512,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O9" t="n">
         <v>142.5962444444444</v>
@@ -8530,7 +8530,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>164.9312690355165</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,10 +8670,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
@@ -8682,10 +8682,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>255.0477063711817</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8752,22 +8752,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>158.9239023638252</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>256.9668982903736</v>
+        <v>256.5734881866366</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>164.3167157393088</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>169.4649313131313</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M21" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9703,16 +9703,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>301.2062135585481</v>
+        <v>244.7225752110828</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9858,10 +9858,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M26" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N26" t="n">
         <v>437.3469244119842</v>
@@ -9940,19 +9940,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,13 +10092,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M29" t="n">
-        <v>449.5135334928325</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N29" t="n">
         <v>437.3469244119842</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,22 +10174,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>369.8170060425004</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>309.6353666274674</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>438.6332444111135</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>182.2394923214954</v>
+        <v>253.1070822390753</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10572,13 +10572,13 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>437.0731727773048</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>380.8001812627454</v>
+        <v>373.6931947635578</v>
       </c>
       <c r="P35" t="n">
         <v>231.2329957552695</v>
@@ -10648,19 +10648,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>218.2437130547859</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>242.3147604003904</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10809,13 +10809,13 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>437.0731727773048</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>380.8001812627454</v>
+        <v>373.6931947635578</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10885,19 +10885,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>222.2855777193561</v>
+        <v>253.5692927615014</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>311.2088090896966</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>276.0422164773723</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>249.2471993224798</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>159.887352254354</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22750,22 +22750,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722618</v>
+        <v>371.3133069426435</v>
       </c>
       <c r="F5" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22832,19 +22832,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22941,19 +22941,19 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R7" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S7" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T7" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U7" t="n">
         <v>286.3190293564909</v>
@@ -22978,13 +22978,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>339.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>331.782241620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
         <v>381.9303700722618</v>
@@ -22999,10 +22999,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>209.8495256553324</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,16 +23023,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U8" t="n">
         <v>251.3456529078365</v>
@@ -23047,7 +23047,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>360.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23069,19 +23069,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>145.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>77.25703415264314</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
         <v>171.6831711038378</v>
@@ -23120,13 +23120,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
-        <v>179.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S10" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23227,16 +23227,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>187.5750895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3456529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23306,16 +23306,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>119.4489211987531</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>90.41568307852349</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23400,7 +23400,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,25 +23418,25 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.88785120902698</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>201.9455894282815</v>
+        <v>202.3252982336507</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V13" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W13" t="n">
-        <v>286.522998336591</v>
+        <v>263.9566458523602</v>
       </c>
       <c r="X13" t="n">
         <v>225.7096553890372</v>
@@ -23455,7 +23455,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
-        <v>365.2728917710076</v>
+        <v>339.6526005763767</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23503,25 +23503,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>228.4448529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>326.6746162331822</v>
       </c>
       <c r="X14" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="15">
@@ -23540,22 +23540,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>134.7442804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>119.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>204.1216209230018</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,19 +23652,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S16" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U16" t="n">
         <v>286.3190293564909</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>382.2136457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>311.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>182.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23737,16 +23737,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>125.5678236918632</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>223.7556276475204</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23816,25 +23816,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>197.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
-        <v>204.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>223.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>181.1105852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23889,31 +23889,31 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>196.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>208.6445625372019</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>258.7290040961748</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W19" t="n">
-        <v>286.522998336591</v>
+        <v>258.9329730762748</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>203.2608960285278</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23938,19 +23938,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>405.0791353121173</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23974,22 +23974,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>128.0146919313124</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
@@ -24008,28 +24008,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,10 +24053,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
@@ -24065,16 +24065,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>26.74647134413024</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24138,7 +24138,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24166,10 +24166,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>363.4759813414134</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24208,22 +24208,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>257.4082506688596</v>
       </c>
       <c r="W23" t="n">
         <v>349.240968717413</v>
@@ -24251,22 +24251,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>22.54023074920468</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>26.16840584907007</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24296,22 +24296,22 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24366,10 +24366,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>130.2684670434959</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24400,22 +24400,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>170.4610416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>194.5906600982693</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
@@ -24466,10 +24466,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24491,7 +24491,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -24500,10 +24500,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24533,7 +24533,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>164.4735779971637</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -24542,13 +24542,13 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24573,7 +24573,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
         <v>162.2271725074396</v>
@@ -24615,7 +24615,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24649,19 +24649,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>10.15237892501841</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24688,7 +24688,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>19.30103642703409</v>
       </c>
       <c r="T29" t="n">
         <v>223.0958495641314</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>386.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>136.7753380837449</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24731,7 +24731,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>61.76086705343042</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24795,7 +24795,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C31" t="n">
         <v>167.2468210986278</v>
@@ -24849,7 +24849,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U31" t="n">
         <v>286.3190293564909</v>
@@ -24877,19 +24877,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>335.4136757674908</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>217.5040457417115</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,10 +24919,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>209.0200695862453</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
@@ -24965,10 +24965,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25007,22 +25007,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>23.74923960493945</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X33" t="n">
-        <v>20.511627104761</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25086,7 +25086,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
@@ -25101,7 +25101,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
-        <v>85.39768576672674</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="35">
@@ -25111,19 +25111,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>203.3525408780254</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>384.0480109801849</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
@@ -25132,10 +25132,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25159,7 +25159,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25247,16 +25247,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>16.40098520347755</v>
+        <v>16.05395204426628</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25281,7 +25281,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756322</v>
       </c>
       <c r="G37" t="n">
         <v>167.9909793584588</v>
@@ -25326,7 +25326,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
-        <v>153.1320617711228</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25354,7 +25354,7 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25366,7 +25366,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>124.4748021157671</v>
+        <v>124.0808044327389</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25402,16 +25402,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>43.71454877867617</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>71.61731896317002</v>
       </c>
       <c r="V38" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
@@ -25484,19 +25484,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X39" t="n">
-        <v>7.083680980781907</v>
+        <v>16.05395204426628</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25518,7 +25518,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F40" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756322</v>
       </c>
       <c r="G40" t="n">
         <v>167.9909793584588</v>
@@ -25530,10 +25530,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J40" t="n">
-        <v>71.32518834398857</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25548,10 +25548,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
         <v>177.2933913771695</v>
@@ -25585,13 +25585,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>194.749750269325</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>141.25877800334</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>202.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
-        <v>155.3510604869632</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,13 +25630,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
@@ -25664,31 +25664,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>126.3749010230265</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25724,16 +25724,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>10.04732596928329</v>
       </c>
     </row>
     <row r="43">
@@ -25764,7 +25764,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I43" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -25800,7 +25800,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>153.1320617711228</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>327897.5868709115</v>
+        <v>350049.7958156169</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350365.0263125472</v>
+        <v>350049.7958156169</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350365.0263125472</v>
+        <v>350049.7958156168</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350365.0263125472</v>
+        <v>350049.7958156169</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352010.6902785869</v>
+        <v>351685.049566824</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506898.8173466545</v>
+        <v>506909.1411107078</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506898.8173466543</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506898.8173466543</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488113.7264674625</v>
+        <v>488398.3911706115</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486668.7194767554</v>
+        <v>486975.2514232369</v>
       </c>
     </row>
     <row r="16">
@@ -26264,43 +26264,43 @@
         <v>59129.07304229552</v>
       </c>
       <c r="C2" t="n">
-        <v>59129.07304229552</v>
+        <v>63121.07616893066</v>
       </c>
       <c r="D2" t="n">
-        <v>63177.88319582793</v>
+        <v>63121.07616893067</v>
       </c>
       <c r="E2" t="n">
-        <v>63177.88319582795</v>
+        <v>63121.07616893067</v>
       </c>
       <c r="F2" t="n">
-        <v>63177.88319582793</v>
+        <v>63121.07616893068</v>
       </c>
       <c r="G2" t="n">
-        <v>63474.44484862834</v>
+        <v>63415.76181874351</v>
       </c>
       <c r="H2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="I2" t="n">
-        <v>91386.509468359</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="J2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="K2" t="n">
-        <v>91386.50946835899</v>
+        <v>88052.58645764725</v>
       </c>
       <c r="L2" t="n">
-        <v>88001.287628359</v>
+        <v>88052.58645764727</v>
       </c>
       <c r="M2" t="n">
-        <v>88001.28762835902</v>
+        <v>88052.58645764725</v>
       </c>
       <c r="N2" t="n">
-        <v>88001.28762835904</v>
+        <v>88052.58645764725</v>
       </c>
       <c r="O2" t="n">
-        <v>87740.8859483589</v>
+        <v>87796.12542771841</v>
       </c>
       <c r="P2" t="n">
         <v>59129.07304229552</v>
@@ -26316,10 +26316,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8277.165051769143</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="D4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="E4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="F4" t="n">
-        <v>11524.36744801407</v>
+        <v>11244.18577987448</v>
       </c>
       <c r="G4" t="n">
-        <v>11581.0330020641</v>
+        <v>11299.21161664248</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026179</v>
+        <v>15899.57777605044</v>
       </c>
       <c r="L4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605044</v>
       </c>
       <c r="M4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605044</v>
       </c>
       <c r="N4" t="n">
-        <v>16267.50248349411</v>
+        <v>15899.57777605044</v>
       </c>
       <c r="O4" t="n">
-        <v>16217.74620066583</v>
+        <v>15851.6895168862</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
     </row>
     <row r="5">
@@ -26420,43 +26420,43 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33627.6</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>15002.70297086521</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>8414.411632653479</v>
       </c>
       <c r="D6" t="n">
-        <v>8368.735747813866</v>
+        <v>16691.57668442264</v>
       </c>
       <c r="E6" t="n">
-        <v>50072.71574781388</v>
+        <v>50319.17668442264</v>
       </c>
       <c r="F6" t="n">
-        <v>50072.71574781386</v>
+        <v>50319.17668442265</v>
       </c>
       <c r="G6" t="n">
-        <v>49642.84184656424</v>
+        <v>49899.20210488045</v>
       </c>
       <c r="H6" t="n">
-        <v>2350.058308097181</v>
+        <v>2628.454590704179</v>
       </c>
       <c r="I6" t="n">
-        <v>59819.37530809721</v>
+        <v>60212.24173303584</v>
       </c>
       <c r="J6" t="n">
-        <v>59819.37530809718</v>
+        <v>60212.24173303583</v>
       </c>
       <c r="K6" t="n">
-        <v>59819.37530809719</v>
+        <v>59057.05362246869</v>
       </c>
       <c r="L6" t="n">
-        <v>58661.78514486489</v>
+        <v>59057.05362246872</v>
       </c>
       <c r="M6" t="n">
-        <v>58661.7851448649</v>
+        <v>59057.05362246869</v>
       </c>
       <c r="N6" t="n">
-        <v>58661.78514486493</v>
+        <v>59057.05362246869</v>
       </c>
       <c r="O6" t="n">
-        <v>58572.73974769307</v>
+        <v>58968.24068289775</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>48630.30297086521</v>
       </c>
     </row>
   </sheetData>
@@ -26730,43 +26730,43 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26916,7 +26916,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26931,10 +26931,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27188,10 +27188,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -34851,22 +34851,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -34936,19 +34936,19 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35012,16 +35012,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,16 +35167,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26.00000000000006</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35337,10 +35337,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35407,22 +35407,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>26.86868686868687</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M21" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36358,16 +36358,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>169.8645014752148</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36516,7 +36516,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M26" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N26" t="n">
         <v>207.9338608153932</v>
@@ -36595,19 +36595,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,13 +36747,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1673002655598</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,22 +36829,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>231.2626262626262</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>167.5013327054491</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>208.2870111838408</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>40.10545839947712</v>
+        <v>110.973048317057</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,13 +37227,13 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>206.726939550032</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>150.7019698410586</v>
+        <v>143.5949833418711</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37303,19 +37303,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>79.68933327491168</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>110.973048317057</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37464,13 +37464,13 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>206.726939550032</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>150.7019698410586</v>
+        <v>143.5949833418711</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37540,19 +37540,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>79.6893332749117</v>
+        <v>110.973048317057</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>91.118958044716</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>45.94400505568559</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>107.1131654004615</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>19.90557816833244</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
